--- a/RRHH/20260508_req18275_boton_venta_planes_colectivos/doc/Estado Final Firmas Anexo Planes Grupales Abril 2026.xlsx
+++ b/RRHH/20260508_req18275_boton_venta_planes_colectivos/doc/Estado Final Firmas Anexo Planes Grupales Abril 2026.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Remu2026\BUK 2026\ABRIL 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\J\RepositorioJ_github\repositorioJ\RRHH\20260508_req18275_boton_venta_planes_colectivos\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10332"/>
   </bookViews>
   <sheets>
     <sheet name="ingresar" sheetId="2" r:id="rId1"/>
@@ -1736,17 +1736,17 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:E116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="5"/>
     <col min="2" max="2" width="35.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="26.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.8984375" style="4" customWidth="1"/>
     <col min="4" max="4" width="11" style="4"/>
     <col min="5" max="5" width="12.5" style="4" customWidth="1"/>
     <col min="6" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>423</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>96658826</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>191080491</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>160180293</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>131294964</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>185753204</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>132361460</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>168654804</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>132528640</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>153615616</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>197486511</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>125964931</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>183572822</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>433</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>79925209</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>160931469</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>144968727</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>104852513</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>119864909</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>91288672</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>434</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>124700361</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>125812759</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>435</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>171051738</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>436</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>108342544</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>118830970</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>154151729</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>164467473</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>153616043</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>437</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>109199915</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>178129899</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>156057517</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>187493722</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>163789116</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>161139238</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>438</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>84492795</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>200005872</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>134408170</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>77156038</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>200987489</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>83367644</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>186976274</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>105097905</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>201100895</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>85760017</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>100304643</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>178345036</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>176764333</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>193105610</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>166217539</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>188481337</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>155407336</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>172526330</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>157845322</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>106451656</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>227018763</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>104081665</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>154048219</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>186895290</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>104368786</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>173059825</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>198577278</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>155418443</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>141203126</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>156321400</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>156095826</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>163914476</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>439</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>81135576</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>114838454</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>134379596</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>150710162</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>164726924</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>270091822</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>164110192</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>167419011</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>178027255</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>168035497</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>134915013</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>124545994</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>176778490</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>182939773</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>136659995</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>122472728</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>135043060</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>163622254</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>116777762</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>162688553</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>174209391</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>177084689</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>120871439</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>125838138</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>124859964</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>129016620</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>154654550</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>204734135</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>186626907</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>130922414</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>169325294</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>109014494</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>105457324</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>213531492</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>193752810</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>156713031</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>192293197</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>158701677</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>137569701</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>179298910</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>89639786</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>107923896</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>131394896</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>155892625</v>
       </c>
@@ -3727,41 +3727,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.375" customWidth="1"/>
-    <col min="2" max="2" width="23.875" customWidth="1"/>
-    <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
-    <col min="5" max="5" width="27.625" customWidth="1"/>
+    <col min="1" max="1" width="21.3984375" customWidth="1"/>
+    <col min="2" max="2" width="23.8984375" customWidth="1"/>
+    <col min="3" max="3" width="15.09765625" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" customWidth="1"/>
+    <col min="5" max="5" width="27.59765625" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="57.125" customWidth="1"/>
-    <col min="8" max="8" width="23.125" customWidth="1"/>
-    <col min="9" max="9" width="21.25" customWidth="1"/>
-    <col min="10" max="10" width="26.125" customWidth="1"/>
+    <col min="7" max="7" width="57.09765625" customWidth="1"/>
+    <col min="8" max="8" width="23.09765625" customWidth="1"/>
+    <col min="9" max="9" width="21.19921875" customWidth="1"/>
+    <col min="10" max="10" width="26.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>420</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>4</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>4</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>4</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>4</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>4</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>4</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>4</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>4</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>4</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>4</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>4</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>4</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>4</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>4</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>4</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>4</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>4</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>4</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>4</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>4</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>4</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>4</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>4</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>4</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>4</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>4</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>4</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>4</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>4</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>4</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>4</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>4</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>4</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>4</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>4</v>
       </c>
@@ -6217,7 +6217,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>4</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>4</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>4</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>4</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>4</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>4</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>4</v>
       </c>
@@ -6441,7 +6441,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>4</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>4</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>4</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>4</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>4</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>4</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>4</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>4</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>4</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>4</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>4</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>4</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>4</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>4</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>4</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>4</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>4</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>4</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>4</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>4</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>4</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>4</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>4</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>4</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>4</v>
       </c>
@@ -7235,7 +7235,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>4</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>4</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>4</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>4</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>4</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>4</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>4</v>
       </c>
@@ -7459,7 +7459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>4</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>4</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>4</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>4</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>4</v>
       </c>
@@ -7619,7 +7619,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>4</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>4</v>
       </c>
